--- a/Новая таблица 5.xlsx
+++ b/Новая таблица 5.xlsx
@@ -1581,6 +1581,9 @@
       <c r="F44" s="0" t="n"/>
       <c r="G44" s="0" t="n"/>
       <c r="H44" s="0" t="n"/>
+      <c r="T44" s="0" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row outlineLevel="0" r="45">
       <c r="A45" s="0" t="n"/>
